--- a/Config_File.xlsx
+++ b/Config_File.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amitg\OneDrive\Documents\UiPath\Property Tax POC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF30FEEE-8F78-41E2-BF90-C2B9DAB2E14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC67A5D-91C9-4C3E-B810-A62D66C81381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{E7DA9AA7-8928-4EE0-8785-33B5CF30111C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E7DA9AA7-8928-4EE0-8785-33B5CF30111C}"/>
   </bookViews>
   <sheets>
     <sheet name="Rule_Config" sheetId="1" r:id="rId1"/>
